--- a/product_selector_out/STM32U3B5-3C5.xlsx
+++ b/product_selector_out/STM32U3B5-3C5.xlsx
@@ -1412,7 +1412,7 @@
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S13" s="4" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S15" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE15" s="4" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE17" s="4" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S18" s="4" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE20" s="4" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AD21" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE21" s="4" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE22" s="4" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5663,109 +5663,109 @@
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>Dual Watchdog, RTC, SysTick</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA26" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD26" s="4" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AE26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF26" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH26" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI26" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ26" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL26" s="4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>Dual Watchdog, RTC, SysTick</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="W26" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X26" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y26" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z26" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA26" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB26" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC26" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD26" s="4" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AE26" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF26" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG26" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH26" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI26" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ26" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK26" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL26" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AM26" s="4" t="inlineStr">
         <is>
           <t>2</t>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S27" s="4" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AD27" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE27" s="4" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6644,109 +6644,109 @@
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>Dual Watchdog, RTC, SysTick</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA29" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD29" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AE29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG29" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH29" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI29" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T29" s="4" t="inlineStr">
-        <is>
-          <t>Dual Watchdog, RTC, SysTick</t>
-        </is>
-      </c>
-      <c r="U29" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="W29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA29" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB29" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD29" s="4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AE29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG29" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH29" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI29" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ29" s="4" t="inlineStr">
+      <c r="AK29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL29" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AK29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL29" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AM29" s="4" t="inlineStr">
         <is>
           <t>2</t>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S30" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="AD30" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE30" s="4" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S31" s="4" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="AD31" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE31" s="4" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7625,109 +7625,109 @@
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>Dual Watchdog, RTC, SysTick</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA32" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD32" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AE32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF32" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI32" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>Dual Watchdog, RTC, SysTick</t>
-        </is>
-      </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA32" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB32" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD32" s="4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AE32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF32" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH32" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI32" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ32" s="4" t="inlineStr">
+      <c r="AK32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL32" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AK32" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL32" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AM32" s="4" t="inlineStr">
         <is>
           <t>2</t>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8708,9 +8708,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="10" t="inlineStr">
@@ -8810,9 +8810,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -8875,19 +8875,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T13" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -8935,9 +8935,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE13" s="8" t="inlineStr">
@@ -8975,9 +8975,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM13" s="6" t="inlineStr">
@@ -9030,24 +9030,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW13" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY13" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ13" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA13" s="6" t="inlineStr">
@@ -9110,9 +9110,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9362,9 +9362,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="10" t="inlineStr">
@@ -9464,9 +9464,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -9529,19 +9529,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T15" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -9589,9 +9589,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE15" s="8" t="inlineStr">
@@ -9629,9 +9629,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM15" s="6" t="inlineStr">
@@ -9684,24 +9684,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW15" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY15" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ15" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA15" s="6" t="inlineStr">
@@ -9764,9 +9764,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9791,9 +9791,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -9856,19 +9856,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T16" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -9916,9 +9916,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE16" s="8" t="inlineStr">
@@ -9956,9 +9956,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM16" s="6" t="inlineStr">
@@ -10011,24 +10011,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY16" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ16" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA16" s="6" t="inlineStr">
@@ -10091,9 +10091,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10118,9 +10118,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -10183,19 +10183,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T17" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -10243,9 +10243,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE17" s="8" t="inlineStr">
@@ -10283,9 +10283,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM17" s="6" t="inlineStr">
@@ -10338,24 +10338,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY17" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ17" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA17" s="6" t="inlineStr">
@@ -10418,9 +10418,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10445,9 +10445,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -10510,19 +10510,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S18" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T18" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -10610,9 +10610,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM18" s="6" t="inlineStr">
@@ -10665,24 +10665,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW18" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY18" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ18" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA18" s="6" t="inlineStr">
@@ -10745,9 +10745,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10772,9 +10772,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -10837,19 +10837,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T19" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -10937,9 +10937,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM19" s="6" t="inlineStr">
@@ -10992,24 +10992,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY19" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ19" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA19" s="6" t="inlineStr">
@@ -11072,9 +11072,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11099,9 +11099,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -11164,19 +11164,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T20" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -11224,9 +11224,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE20" s="8" t="inlineStr">
@@ -11264,9 +11264,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM20" s="6" t="inlineStr">
@@ -11319,24 +11319,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW20" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY20" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ20" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA20" s="6" t="inlineStr">
@@ -11399,9 +11399,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11426,9 +11426,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -11491,19 +11491,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R21" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S21" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T21" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -11551,9 +11551,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE21" s="8" t="inlineStr">
@@ -11591,9 +11591,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM21" s="6" t="inlineStr">
@@ -11646,24 +11646,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW21" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY21" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ21" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA21" s="6" t="inlineStr">
@@ -11726,9 +11726,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11753,9 +11753,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -11818,19 +11818,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T22" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
@@ -11878,9 +11878,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE22" s="8" t="inlineStr">
@@ -11918,9 +11918,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM22" s="6" t="inlineStr">
@@ -11973,24 +11973,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW22" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY22" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ22" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA22" s="6" t="inlineStr">
@@ -12053,9 +12053,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12080,9 +12080,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -12145,14 +12145,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R23" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -12300,24 +12300,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW23" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY23" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ23" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA23" s="6" t="inlineStr">
@@ -12380,9 +12380,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12407,9 +12407,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -12472,14 +12472,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R24" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -12627,24 +12627,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW24" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY24" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ24" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA24" s="6" t="inlineStr">
@@ -12707,9 +12707,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12734,9 +12734,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -12799,19 +12799,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T25" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -12899,9 +12899,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM25" s="6" t="inlineStr">
@@ -12954,24 +12954,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW25" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY25" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ25" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA25" s="6" t="inlineStr">
@@ -13034,9 +13034,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13061,9 +13061,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -13126,19 +13126,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R26" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S26" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T26" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -13226,9 +13226,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM26" s="6" t="inlineStr">
@@ -13281,24 +13281,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW26" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY26" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ26" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA26" s="6" t="inlineStr">
@@ -13361,9 +13361,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13388,9 +13388,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -13453,19 +13453,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R27" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S27" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T27" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U27" s="6" t="inlineStr">
@@ -13513,9 +13513,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE27" s="8" t="inlineStr">
@@ -13553,9 +13553,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM27" s="6" t="inlineStr">
@@ -13608,24 +13608,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW27" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY27" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ27" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA27" s="6" t="inlineStr">
@@ -13688,9 +13688,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13715,9 +13715,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -13780,14 +13780,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R28" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -13935,24 +13935,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW28" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY28" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ28" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA28" s="6" t="inlineStr">
@@ -14015,9 +14015,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14042,9 +14042,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -14107,19 +14107,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R29" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S29" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T29" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
@@ -14207,9 +14207,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM29" s="6" t="inlineStr">
@@ -14262,24 +14262,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW29" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY29" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ29" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA29" s="6" t="inlineStr">
@@ -14342,9 +14342,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14369,9 +14369,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -14434,19 +14434,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R30" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S30" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T30" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
@@ -14494,9 +14494,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE30" s="8" t="inlineStr">
@@ -14534,9 +14534,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM30" s="6" t="inlineStr">
@@ -14589,24 +14589,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW30" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY30" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ30" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA30" s="6" t="inlineStr">
@@ -14669,9 +14669,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -14696,9 +14696,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -14761,19 +14761,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R31" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S31" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T31" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U31" s="6" t="inlineStr">
@@ -14821,9 +14821,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE31" s="8" t="inlineStr">
@@ -14861,9 +14861,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM31" s="6" t="inlineStr">
@@ -14916,24 +14916,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW31" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY31" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ31" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA31" s="6" t="inlineStr">
@@ -14996,9 +14996,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15023,9 +15023,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -15088,19 +15088,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R32" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S32" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T32" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="T32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
@@ -15188,9 +15188,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM32" s="6" t="inlineStr">
@@ -15243,24 +15243,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW32" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY32" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ32" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA32" s="6" t="inlineStr">
@@ -15323,9 +15323,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15344,7 +15344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -15449,7 +15449,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -15459,19 +15459,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -15481,19 +15481,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -15503,19 +15503,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -15525,19 +15525,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -15559,7 +15559,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -15590,1700 +15590,6 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32U3C5CI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32U3C5CI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZI</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZI</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32U3C5ZI</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32U3C5ZI</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32U3C5ZI</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32U3C5ZI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32U3C5QI</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32U3C5QI</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32U3C5QI</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32U3C5QI</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32U3B5WG</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32U3B5WG</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32U3B5WG</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32U3B5WG</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
         <is>
           <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>

--- a/product_selector_out/STM32U3B5-3C5.xlsx
+++ b/product_selector_out/STM32U3B5-3C5.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE12" s="4" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE14" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE15" s="4" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE17" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="AD19" s="4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AE19" s="4" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE20" s="4" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AD21" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE21" s="4" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE22" s="4" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AD25" s="4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AE25" s="4" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="AD26" s="4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE26" s="4" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AD27" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE27" s="4" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="AD29" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE29" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="AD30" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE30" s="4" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="AD31" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE31" s="4" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="AD32" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE32" s="4" t="inlineStr">
@@ -10570,9 +10570,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE18" s="8" t="inlineStr">
@@ -10897,9 +10897,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE19" s="8" t="inlineStr">
@@ -12859,9 +12859,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE25" s="8" t="inlineStr">
@@ -13186,9 +13186,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE26" s="8" t="inlineStr">
@@ -14167,9 +14167,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE29" s="8" t="inlineStr">
@@ -15148,9 +15148,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE32" s="8" t="inlineStr">

--- a/product_selector_out/STM32U3B5-3C5.xlsx
+++ b/product_selector_out/STM32U3B5-3C5.xlsx
@@ -8653,9 +8653,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN12" s="6" t="inlineStr">
@@ -8980,9 +8980,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN13" s="6" t="inlineStr">
@@ -9307,9 +9307,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN14" s="6" t="inlineStr">
@@ -9634,9 +9634,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -9961,9 +9961,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr">
@@ -10288,9 +10288,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">
@@ -10615,9 +10615,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -10942,9 +10942,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN19" s="6" t="inlineStr">
@@ -11269,9 +11269,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -11596,9 +11596,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -11923,9 +11923,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN22" s="6" t="inlineStr">
@@ -12904,9 +12904,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN25" s="6" t="inlineStr">
@@ -13231,9 +13231,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN26" s="6" t="inlineStr">
@@ -13558,9 +13558,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN27" s="6" t="inlineStr">
@@ -14212,9 +14212,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN29" s="6" t="inlineStr">
@@ -14539,9 +14539,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN30" s="6" t="inlineStr">
@@ -14866,9 +14866,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN31" s="6" t="inlineStr">
@@ -15193,9 +15193,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN32" s="6" t="inlineStr">

--- a/product_selector_out/STM32U3B5-3C5.xlsx
+++ b/product_selector_out/STM32U3B5-3C5.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM32"/>
+  <dimension ref="A1:BN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.31640625" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -7860,12 +7967,17 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -7886,16 +7998,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -7908,6 +8018,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -7927,7 +8038,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -7965,7 +8078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM32"/>
+  <dimension ref="A1:BN32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8033,6 +8146,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8366,6 +8480,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -8461,6 +8580,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8783,7 +8903,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9110,7 +9235,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9437,7 +9567,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9764,7 +9899,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10091,7 +10231,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10418,7 +10563,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10745,7 +10895,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11072,7 +11227,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11399,7 +11559,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11726,7 +11891,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12053,7 +12223,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12380,7 +12555,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12707,7 +12887,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13034,7 +13219,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13361,7 +13551,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13688,7 +13883,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14015,7 +14215,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14342,7 +14547,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14669,7 +14879,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14996,7 +15211,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15323,7 +15543,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15331,8 +15556,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
